--- a/data/export/2026-09-16-浦东78路.xlsx
+++ b/data/export/2026-09-16-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,22 +819,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -986,27 +986,31 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>109分钟</t>
+          <t>111分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:50采样，终点ETA 39分钟</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1014,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1038,12 +1042,12 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1053,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -1106,26 +1110,22 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:30采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1172,22 +1172,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,22 +1291,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1349,19 +1349,19 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>113分钟</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站五莲路荷泽路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1395,12 +1395,12 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -1458,27 +1458,31 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1486,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1510,33 +1514,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -1574,19 +1582,19 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站张杨北路五莲路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±12分钟</t>
+          <t>同车下一次反向发车09:10，减去该车自身同类时段历史终点停站中位数12分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1601,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1630,7 +1638,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1640,17 +1648,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1693,26 +1701,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数105分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:50采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -1720,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1749,7 +1753,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1759,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -1807,29 +1811,29 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金高路源华路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1863,12 +1867,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1878,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -1926,27 +1930,31 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>111分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1954,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1978,33 +1986,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>96.5</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -2037,29 +2049,29 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站航津路地铁站 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2069,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2093,12 +2105,12 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2118,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -2156,29 +2168,29 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站五莲路东陆路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2188,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2212,12 +2224,12 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2227,22 +2239,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -2275,24 +2287,24 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站航津路地铁站 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2307,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2331,12 +2343,12 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2346,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -2404,21 +2416,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数96分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:30采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2426,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2455,7 +2463,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2475,12 +2483,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -2513,29 +2521,29 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2545,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2569,12 +2577,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2594,12 +2602,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -2632,27 +2640,31 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2660,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2684,37 +2696,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2734,7 @@
       <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2747,39 +2759,39 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2793,22 +2805,22 @@
       <c r="T20" s="2" t="inlineStr"/>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>计划发车</t>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2818,22 +2830,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2853,7 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2851,7 +2863,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2866,39 +2878,39 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2912,22 +2924,22 @@
       <c r="T21" s="2" t="inlineStr"/>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+          <t>计划发车</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2937,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2982,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3013,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3027,7 +3039,7 @@
       <c r="T22" s="2" t="inlineStr"/>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -3052,22 +3064,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -3100,24 +3112,24 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -3132,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3156,12 +3168,12 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3171,22 +3183,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -3194,24 +3206,24 @@
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3224,30 +3236,30 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：10:10采样，终点ETA 6分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3261,43 +3273,2173 @@
       <c r="T24" s="2" t="inlineStr"/>
       <c r="U24" s="2" t="inlineStr">
         <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>16/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>9/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>3/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>10/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：10:30采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>5/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>2/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>10:30采样：该车到重点站和龙路花山路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数6分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>96.5</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>13/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：10:30采样，终点ETA 40分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>7/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>10:30采样：该车到重点站金高路东靖路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>8/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>10:30采样：该车到重点站金高路行泰路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>94.7</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>11/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>10:30采样：该车到重点站金高路东靖路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>4/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>10:30采样：该车到重点站杨高北路（外高桥保税区南站） ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>15/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>10:30采样：该车到重点站金杨路云山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>5/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>3/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>9/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>5/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>2/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>7/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X24" s="2" t="inlineStr">
+      <c r="X42" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="Y42" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z24" s="2" t="inlineStr">
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>—/17</t>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>96.5</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>13/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-16-浦东78路.xlsx
+++ b/data/export/2026-09-16-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,22 +2239,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,22 +2711,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,17 +2830,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,22 +3064,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,22 +3532,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -3704,19 +3704,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:30采样，终点ETA 19分钟</t>
+          <t>SHMAAS末次终点ETA推算：10:40采样，终点ETA 6分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,22 +3885,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -3933,29 +3933,29 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10:30采样：该车到重点站和龙路花山路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数6分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4004,22 +4004,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -4052,27 +4052,31 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:30采样，终点ETA 40分钟</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4080,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4104,12 +4108,12 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4119,22 +4123,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -4167,29 +4171,29 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10:30采样：该车到重点站金高路东靖路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4199,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4223,12 +4227,12 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4248,12 +4252,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -4286,24 +4290,24 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10:30采样：该车到重点站金高路行泰路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -4318,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4342,12 +4346,12 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4357,17 +4361,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4405,29 +4409,29 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10:30采样：该车到重点站金高路东靖路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4437,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4461,12 +4465,12 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4476,22 +4480,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -4524,29 +4528,29 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10:30采样：该车到重点站杨高北路（外高桥保税区南站） ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4556,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4580,12 +4584,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4595,22 +4599,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -4648,19 +4652,19 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10:30采样：该车到重点站金杨路云山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>10:50采样：该车到重点站五莲路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -4675,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4724,12 +4728,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -4762,29 +4766,29 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4794,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4818,12 +4822,12 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4833,22 +4837,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -4881,29 +4885,29 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4913,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4937,12 +4941,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4952,22 +4956,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -5000,29 +5004,29 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5032,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5056,12 +5060,12 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5071,22 +5075,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -5119,24 +5123,24 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -5151,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5175,12 +5179,12 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5190,22 +5194,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -5238,29 +5242,29 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±6分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5270,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5294,12 +5298,12 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5309,22 +5313,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -5357,27 +5361,31 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5385,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5409,37 +5417,1215 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>8/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>92.8</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>11/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>6/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>12:40采样：该车到重点站五莲路荷泽路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>9/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>12:40采样：该车到重点站金高路俱进路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>5/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>12:40采样：该车到重点站金杨路枣庄路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>92.2</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>10/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
+      <c r="X48" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="Y48" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>96.5</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>13/17</t>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>4/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>1/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>3/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>8/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>92.8</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>11/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-16-浦东78路.xlsx
+++ b/data/export/2026-09-16-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,22 +819,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,17 +938,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,22 +1172,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,14 +1291,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>89.7</t>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,22 +1648,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,17 +1763,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,17 +2239,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,22 +2473,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,22 +2592,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,22 +2830,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,22 +3064,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>89.7</t>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,22 +3298,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,22 +3532,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,22 +3651,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,22 +4004,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4242,22 +4242,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4361,22 +4361,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4480,17 +4480,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4599,22 +4599,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -4642,90 +4642,98 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq22推进至seq36，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10:50采样：该车到重点站五莲路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>五莲路东陆路</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>06:30</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>计划发车</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t>同车重点站剩余时间</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="AA36" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>89.7</t>
@@ -4733,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,22 +4845,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4956,22 +4964,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5075,22 +5083,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5194,17 +5202,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5274,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5313,17 +5321,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5366,24 +5374,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5393,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5432,22 +5440,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -5485,12 +5493,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -5512,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5551,22 +5559,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -5604,24 +5612,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5631,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5670,17 +5678,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5718,29 +5726,29 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站五莲路荷泽路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5750,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5774,12 +5782,12 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5789,22 +5797,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -5842,26 +5850,22 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站金高路俱进路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:40采样，终点ETA 6分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5869,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5898,7 +5902,7 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5908,22 +5912,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -5956,29 +5960,29 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站金杨路枣庄路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±10分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5988,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6012,12 +6016,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6027,22 +6031,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -6075,27 +6079,31 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -6103,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6127,37 +6135,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -6190,27 +6198,31 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -6218,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6242,32 +6254,32 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6305,29 +6317,29 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6337,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6361,12 +6373,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6376,17 +6388,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6424,12 +6436,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -6441,12 +6453,12 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6456,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6480,12 +6492,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6495,22 +6507,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -6543,27 +6555,31 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6571,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6595,37 +6611,4372 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>87.8</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>7/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>6/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>95.4</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>15/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>8/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>16/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>14/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>13/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>1/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>5/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>17/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>3/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>4/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>11/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>89.7</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>10/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>88.8</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>9/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>87.8</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>7/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>11/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>95.4</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>15/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>6/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>103分钟</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>16/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>105分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>8/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：17:50采样，终点ETA 20分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>14/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>104分钟</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：17:40采样，终点ETA 39分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>13/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X52" s="2" t="inlineStr">
+      <c r="X75" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y52" s="2" t="inlineStr">
+      <c r="Y75" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z52" s="2" t="inlineStr">
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>1/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>3/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB52" s="2" t="inlineStr">
-        <is>
-          <t>92.8</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>17/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>4/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
         <is>
           <t>11/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>5/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>88.8</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>9/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>11/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>87.8</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>7/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>6/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>89.7</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>10/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>8/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>95.4</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>15/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>16/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>13/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-16-浦东78路.xlsx
+++ b/data/export/2026-09-16-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,22 +1291,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,22 +1648,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,22 +2473,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,17 +2592,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3069,17 +3069,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3183,22 +3183,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,17 +3298,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,17 +3537,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,22 +3651,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,17 +3766,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,22 +3885,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,17 +4009,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4128,12 +4128,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4242,22 +4242,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4366,17 +4366,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4485,12 +4485,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4604,17 +4604,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,22 +4726,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4850,17 +4850,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,17 +5083,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5202,22 +5202,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5564,17 +5564,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,17 +5917,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,17 +6150,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6512,17 +6512,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6631,17 +6631,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6869,17 +6869,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6988,17 +6988,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7102,22 +7102,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7459,22 +7459,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7578,17 +7578,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7697,17 +7697,17 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7935,17 +7935,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8054,22 +8054,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8173,22 +8173,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,17 +8297,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8416,17 +8416,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8530,22 +8530,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8654,17 +8654,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8821,24 +8821,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8887,22 +8887,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -9054,27 +9054,31 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:50采样，终点ETA 20分钟</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9082,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9106,12 +9110,12 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9131,7 +9135,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9169,27 +9173,31 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:40采样，终点ETA 39分钟</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -9197,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9221,12 +9229,12 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9241,12 +9249,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9284,27 +9292,31 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9312,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9336,37 +9348,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -9399,27 +9411,31 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9427,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9451,17 +9467,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9471,12 +9487,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9514,27 +9530,31 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -9542,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9566,32 +9586,32 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9629,27 +9649,31 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9657,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9681,32 +9705,32 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9744,27 +9768,31 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9772,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9796,37 +9824,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -9859,27 +9887,31 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9887,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9911,32 +9943,32 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -9974,27 +10006,31 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>111分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10002,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10026,17 +10062,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10046,17 +10082,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -10089,27 +10125,31 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10117,7 +10157,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10141,37 +10181,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -10204,27 +10244,31 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10232,7 +10276,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10256,17 +10300,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10276,17 +10320,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -10324,19 +10368,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 8分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
@@ -10347,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10371,17 +10415,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10391,12 +10435,12 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10434,27 +10478,31 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10462,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10486,37 +10534,37 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA85" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -10554,19 +10602,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：19:30采样，终点ETA 7分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr"/>
@@ -10577,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10601,17 +10649,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10621,17 +10669,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -10664,27 +10712,31 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10692,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10716,17 +10768,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10736,17 +10788,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -10784,19 +10836,19 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：19:30采样，终点ETA 24分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr"/>
@@ -10807,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10831,37 +10883,37 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -10894,27 +10946,31 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -10922,7 +10978,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10946,37 +11002,1338 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>13/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：19:50采样，终点ETA 6分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>83.4</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>2/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>4/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>97.8</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>17/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>87.9</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>5/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>10/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>90.6</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>9/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>21:25</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>10/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>21:49</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>20:50采样：该车到重点站金高路源华路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>94.8</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>14/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X89" s="2" t="inlineStr">
+      <c r="X98" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y89" s="2" t="inlineStr">
+      <c r="Y98" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z89" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA89" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB89" s="2" t="inlineStr">
-        <is>
-          <t>94.3</t>
-        </is>
-      </c>
-      <c r="AC89" s="2" t="inlineStr">
-        <is>
-          <t>13/17</t>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>97.8</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>17/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>10/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>23:04</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>10/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-16-浦东78路.xlsx
+++ b/data/export/2026-09-16-浦东78路.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7702,17 +7702,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9606,17 +9606,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -10157,7 +10157,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11375,17 +11375,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11780,24 +11780,24 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>21:25</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -11894,29 +11894,29 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>20:50采样：该车到重点站金高路源华路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -11975,12 +11975,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -12013,27 +12013,31 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12041,7 +12045,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12065,17 +12069,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12085,17 +12089,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -12133,24 +12137,24 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±13分钟</t>
+          <t>21:20采样：该车到重点站金杨路枣庄路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12160,7 +12164,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12184,12 +12188,12 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
@@ -12209,7 +12213,7 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12279,7 +12283,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12328,12 +12332,12 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-16-浦东78路.xlsx
+++ b/data/export/2026-09-16-浦东78路.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>五莲路东陆路</t>
+          <t>五莲路荷泽路</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
@@ -4696,7 +4696,7 @@
       <c r="S36" s="2" t="inlineStr"/>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>区间折返已由主分类器确认；现有采样不足以把折返发车时间控制在±10分钟</t>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq16映射；现有采样不足以把折返发车时间控制在±10分钟</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11899,12 +11899,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11975,12 +11975,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -12018,24 +12018,24 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">

--- a/data/export/2026-09-16-浦东78路.xlsx
+++ b/data/export/2026-09-16-浦东78路.xlsx
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -12018,24 +12018,24 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>22:04</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12132,29 +12132,29 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站金杨路枣庄路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12188,12 +12188,12 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -12268,7 +12268,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>21:50采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
